--- a/events/Copenhagen_2021_WCH/Copenhagen_2021_WCH_Results.xlsx
+++ b/events/Copenhagen_2021_WCH/Copenhagen_2021_WCH_Results.xlsx
@@ -5170,6 +5170,11 @@
           <t>36313</t>
         </is>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
       <c r="X73" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -19239,6 +19244,11 @@
           <t>36313</t>
         </is>
       </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
       <c r="X277" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -77064,6 +77074,11 @@
       </c>
       <c r="L1097" t="n">
         <v>8</v>
+      </c>
+      <c r="R1097" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
       </c>
       <c r="S1097" t="inlineStr">
         <is>
@@ -94372,7 +94387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D423"/>
+  <dimension ref="A1:D424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103681,6 +103696,28 @@
         </is>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Anja</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>OSTERMAN</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
